--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484344_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484344_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.261</v>
+        <v>7.9559</v>
       </c>
       <c r="E2" t="n">
-        <v>3.9153</v>
+        <v>4.5013</v>
       </c>
       <c r="F2" t="n">
-        <v>3.3457</v>
+        <v>3.4546</v>
       </c>
       <c r="G2" t="n">
         <v>6.7709</v>
@@ -610,13 +610,13 @@
         <v>2.3441</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5601</v>
+        <v>0.1348</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0289</v>
+        <v>-0.4429</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4687</v>
+        <v>0.5777</v>
       </c>
       <c r="V2" t="n">
         <v>-0.1219</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.9285</v>
+        <v>6.3473</v>
       </c>
       <c r="E3" t="n">
-        <v>4.7183</v>
+        <v>5.001</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2102</v>
+        <v>1.3463</v>
       </c>
       <c r="G3" t="n">
         <v>4.8968</v>
@@ -688,13 +688,13 @@
         <v>2.7348</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3191</v>
+        <v>0.0998</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.839</v>
+        <v>-0.5563</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5199</v>
+        <v>0.656</v>
       </c>
       <c r="V3" t="n">
         <v>0.7647</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.6488</v>
+        <v>4.3903</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2645</v>
+        <v>1.2239</v>
       </c>
       <c r="F4" t="n">
-        <v>3.3843</v>
+        <v>3.1664</v>
       </c>
       <c r="G4" t="n">
         <v>2.1828</v>
@@ -766,13 +766,13 @@
         <v>3.3208</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8782</v>
+        <v>0.6197</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0772</v>
+        <v>0.0366</v>
       </c>
       <c r="U4" t="n">
-        <v>0.801</v>
+        <v>0.5831</v>
       </c>
       <c r="V4" t="n">
         <v>-0.3656</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.8589</v>
+        <v>2.9743</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8166</v>
+        <v>1.0682</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0423</v>
+        <v>1.9061</v>
       </c>
       <c r="G5" t="n">
         <v>1.2087</v>
@@ -844,13 +844,13 @@
         <v>2.7348</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1088</v>
+        <v>0.2242</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4487</v>
+        <v>-0.2997</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6601</v>
+        <v>0.5239</v>
       </c>
       <c r="V5" t="n">
         <v>-0.0213</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.5555</v>
+        <v>2.6221</v>
       </c>
       <c r="E6" t="n">
-        <v>2.2412</v>
+        <v>2.3623</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3143</v>
+        <v>0.2599</v>
       </c>
       <c r="G6" t="n">
         <v>2.7657</v>
@@ -922,13 +922,13 @@
         <v>1.3674</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3406</v>
+        <v>0.4072</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0522</v>
+        <v>0.0689</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3928</v>
+        <v>0.3383</v>
       </c>
       <c r="V6" t="n">
         <v>-0.9414</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. BELVER EDO</t>
+          <t>A. SOTO CAPARROS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0839</v>
+        <v>0.8279</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3723</v>
+        <v>-1.8977</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4561</v>
+        <v>2.7256</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3119</v>
+        <v>-1.157</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5513</v>
+        <v>-1.9658</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8632</v>
+        <v>0.8087</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0568</v>
+        <v>-0.8625</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0025</v>
+        <v>-1.6718</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0543</v>
+        <v>0.8093</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2551</v>
+        <v>-0.2945</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5538</v>
+        <v>-0.2939</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8089</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1953</v>
+        <v>1.3674</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1721</v>
+        <v>-1.3674</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3674</v>
+        <v>2.7348</v>
       </c>
       <c r="S7" t="n">
-        <v>1.5264</v>
+        <v>-0.6224</v>
       </c>
       <c r="T7" t="n">
-        <v>0.743</v>
+        <v>-0.8864</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7835</v>
+        <v>0.264</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.9498</v>
+        <v>1.24</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.9498</v>
+        <v>0.0213</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. SOTO CAPARROS</t>
+          <t>M. PAGES SAUQUE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0106</v>
+        <v>-0.4088</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.4638</v>
+        <v>-0.9546</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4533</v>
+        <v>0.5458</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.157</v>
+        <v>-1.0148</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.9658</v>
+        <v>-1.2712</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8087</v>
+        <v>0.2564</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.8625</v>
+        <v>-0.93</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.6718</v>
+        <v>-0.9171</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8093</v>
+        <v>-0.0128</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2945</v>
+        <v>-0.0848</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2939</v>
+        <v>-0.354</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.2692</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3674</v>
+        <v>0.7814</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.3674</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.7348</v>
+        <v>0.7814</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.4609</v>
+        <v>-0.1754</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.4525</v>
+        <v>-0.3019</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0083</v>
+        <v>0.1265</v>
       </c>
       <c r="V8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2186</v>
+        <v>0.2772</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0213</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. PAGES SAUQUE</t>
+          <t>I. BELVER EDO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0511</v>
+        <v>-0.8297</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.379</v>
+        <v>-0.959</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3279</v>
+        <v>0.1293</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.0148</v>
+        <v>0.3119</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.2712</v>
+        <v>-0.5513</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2564</v>
+        <v>0.8632</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.93</v>
+        <v>0.0568</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.9171</v>
+        <v>0.0025</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0128</v>
+        <v>0.0543</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0848</v>
+        <v>0.2551</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.354</v>
+        <v>-0.5538</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2692</v>
+        <v>0.8089</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7814</v>
+        <v>0.1953</v>
       </c>
       <c r="Q9" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.6128</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.1562</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.4566</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-1.9498</v>
+      </c>
+      <c r="W9" t="n">
         <v>0</v>
       </c>
-      <c r="R9" t="n">
-        <v>0.7814</v>
-      </c>
-      <c r="S9" t="n">
-        <v>-0.8177</v>
-      </c>
-      <c r="T9" t="n">
-        <v>-0.7262999999999999</v>
-      </c>
-      <c r="U9" t="n">
-        <v>-0.0914</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0.2772</v>
-      </c>
       <c r="X9" t="n">
-        <v>-0.2772</v>
+        <v>-1.9498</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.8476</v>
+        <v>-3.6181</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6144</v>
+        <v>-2.4121</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2332</v>
+        <v>-1.206</v>
       </c>
       <c r="G10" t="n">
         <v>-2.3958</v>
@@ -1234,13 +1234,13 @@
         <v>1.3674</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8843</v>
+        <v>-0.6548</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8473000000000001</v>
+        <v>-0.6451</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0369</v>
+        <v>-0.0097</v>
       </c>
       <c r="V10" t="n">
         <v>-1.7396</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.7604</v>
+        <v>-5.6865</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.5031</v>
+        <v>-6.4019</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7427</v>
+        <v>0.7155</v>
       </c>
       <c r="G11" t="n">
         <v>-4.7776</v>
@@ -1312,13 +1312,13 @@
         <v>1.7581</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3483</v>
+        <v>-0.2744</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4758</v>
+        <v>-0.3747</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1275</v>
+        <v>0.1003</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2437</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>13.6669</v>
+        <v>14.5747</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6233000000000004</v>
+        <v>1.531399999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>13.0436</v>
+        <v>13.0435</v>
       </c>
       <c r="G12" t="n">
         <v>8.791600000000001</v>
@@ -1390,13 +1390,13 @@
         <v>20.511</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5363999999999998</v>
+        <v>0.3714999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.1531</v>
+        <v>-3.2453</v>
       </c>
       <c r="U12" t="n">
-        <v>3.6169</v>
+        <v>3.6167</v>
       </c>
       <c r="V12" t="n">
         <v>-3.3786</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C. VIDAL AGRA</t>
+          <t>G. SABATÉS SALA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.8915</v>
+        <v>2.5716</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1927</v>
+        <v>1.3646</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6989</v>
+        <v>1.2071</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0867</v>
+        <v>1.1088</v>
       </c>
       <c r="H13" t="n">
-        <v>1.045</v>
+        <v>0.7583</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.9583</v>
+        <v>0.3506</v>
       </c>
       <c r="J13" t="n">
-        <v>0.986</v>
+        <v>1.3384</v>
       </c>
       <c r="K13" t="n">
-        <v>0.8646</v>
+        <v>0.7176</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1214</v>
+        <v>0.6208</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.8994</v>
+        <v>-0.2295</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1804</v>
+        <v>0.0407</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.0797</v>
+        <v>-0.2702</v>
       </c>
       <c r="P13" t="n">
-        <v>0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9767</v>
+        <v>-0.1953</v>
       </c>
       <c r="R13" t="n">
-        <v>1.7581</v>
+        <v>1.3674</v>
       </c>
       <c r="S13" t="n">
-        <v>2.6914</v>
+        <v>-0.474</v>
       </c>
       <c r="T13" t="n">
-        <v>1.574</v>
+        <v>-0.665</v>
       </c>
       <c r="U13" t="n">
-        <v>1.1174</v>
+        <v>0.1911</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3321</v>
+        <v>0.7647</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6093</v>
+        <v>0.8865</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2772</v>
+        <v>-0.1219</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. SABATÉS SALA</t>
+          <t>C. VIDAL AGRA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.35</v>
+        <v>2.1569</v>
       </c>
       <c r="E14" t="n">
-        <v>1.0612</v>
+        <v>0.6758999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2888</v>
+        <v>1.481</v>
       </c>
       <c r="G14" t="n">
-        <v>1.1088</v>
+        <v>0.0867</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7583</v>
+        <v>1.045</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3506</v>
+        <v>-0.9583</v>
       </c>
       <c r="J14" t="n">
-        <v>1.3384</v>
+        <v>0.986</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7176</v>
+        <v>0.8646</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6208</v>
+        <v>0.1214</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.2295</v>
+        <v>-0.8994</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0407</v>
+        <v>0.1804</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2702</v>
+        <v>-1.0797</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.1953</v>
+        <v>-0.9767</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3674</v>
+        <v>1.7581</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6956</v>
+        <v>0.9568</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9684</v>
+        <v>0.0573</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2728</v>
+        <v>0.8995</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7647</v>
+        <v>0.3321</v>
       </c>
       <c r="W14" t="n">
-        <v>0.8865</v>
+        <v>0.6093</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1219</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7211</v>
+        <v>0.8378</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.0655</v>
+        <v>-1.1666</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7866</v>
+        <v>2.0045</v>
       </c>
       <c r="G15" t="n">
         <v>1.0178</v>
@@ -1624,13 +1624,13 @@
         <v>1.3674</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2196</v>
+        <v>0.3363</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.22</v>
+        <v>-0.3211</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4395</v>
+        <v>0.6574</v>
       </c>
       <c r="V15" t="n">
         <v>0.2651</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.5563</v>
+        <v>-0.6768</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6851</v>
+        <v>1.4829</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.2414</v>
+        <v>-2.1597</v>
       </c>
       <c r="G16" t="n">
         <v>-1.6477</v>
@@ -1702,13 +1702,13 @@
         <v>0.586</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0215</v>
+        <v>-0.099</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.22</v>
+        <v>-0.4222</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2415</v>
+        <v>0.3232</v>
       </c>
       <c r="V16" t="n">
         <v>2.4373</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6535</v>
+        <v>-0.7352</v>
       </c>
       <c r="E17" t="n">
         <v>-0.0801</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5734</v>
+        <v>-0.6551</v>
       </c>
       <c r="G17" t="n">
         <v>-0.5034</v>
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1271</v>
+        <v>0.0454</v>
       </c>
       <c r="T17" t="n">
         <v>-0.121</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2481</v>
+        <v>0.1664</v>
       </c>
       <c r="V17" t="n">
         <v>-0.2772</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1548</v>
+        <v>-1.1395</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3218</v>
+        <v>-0.8162</v>
       </c>
       <c r="F18" t="n">
-        <v>0.167</v>
+        <v>-0.3233</v>
       </c>
       <c r="G18" t="n">
         <v>-0.4847</v>
@@ -1858,13 +1858,13 @@
         <v>1.3674</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0609</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0756</v>
+        <v>-0.5701000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>1.1366</v>
+        <v>0.6463</v>
       </c>
       <c r="V18" t="n">
         <v>0.8317</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8369</v>
+        <v>-1.5996</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.9973</v>
+        <v>-1.8962</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1604</v>
+        <v>0.2966</v>
       </c>
       <c r="G19" t="n">
         <v>-0.8299</v>
@@ -1936,13 +1936,13 @@
         <v>0.586</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6163</v>
+        <v>-0.379</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4704</v>
+        <v>-0.3693</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1459</v>
+        <v>-0.0097</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1196</v>
+        <v>-1.9991</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.977</v>
+        <v>-1.7748</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1426</v>
+        <v>-0.2243</v>
       </c>
       <c r="G20" t="n">
         <v>-1.9771</v>
@@ -2014,13 +2014,13 @@
         <v>0.586</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2481</v>
+        <v>0.3687</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4566</v>
+        <v>-0.2544</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7048</v>
+        <v>0.6231</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2103</v>
+        <v>-2.0898</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.7131</v>
+        <v>-2.5108</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5028</v>
+        <v>0.4211</v>
       </c>
       <c r="G21" t="n">
         <v>-0.5785</v>
@@ -2092,13 +2092,13 @@
         <v>1.1721</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5332</v>
+        <v>-0.4127</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6052</v>
+        <v>-0.403</v>
       </c>
       <c r="U21" t="n">
-        <v>0.07199999999999999</v>
+        <v>-0.0097</v>
       </c>
       <c r="V21" t="n">
         <v>-0.1219</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.4714</v>
+        <v>-5.1251</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.5279</v>
+        <v>-4.4268</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9434</v>
+        <v>-0.6983</v>
       </c>
       <c r="G22" t="n">
         <v>-3.0319</v>
@@ -2170,13 +2170,13 @@
         <v>1.9534</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.07870000000000001</v>
+        <v>0.2676</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5226</v>
+        <v>-0.4215</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4439</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="V22" t="n">
         <v>0.7647</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.6267</v>
+        <v>-5.8682</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.2999</v>
+        <v>-3.8954</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.3268</v>
+        <v>-1.9728</v>
       </c>
       <c r="G23" t="n">
         <v>-1.9517</v>
@@ -2248,13 +2248,13 @@
         <v>0.9767</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9085</v>
+        <v>-0.15</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5309</v>
+        <v>-0.1265</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3775</v>
+        <v>-0.0235</v>
       </c>
       <c r="V23" t="n">
         <v>-1.6177</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-13.6669</v>
+        <v>-13.667</v>
       </c>
       <c r="E24" t="n">
-        <v>-13.0436</v>
+        <v>-13.0435</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.6230999999999995</v>
+        <v>-0.6231999999999995</v>
       </c>
       <c r="G24" t="n">
         <v>-8.791600000000001</v>
@@ -2326,13 +2326,13 @@
         <v>11.7205</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5362999999999999</v>
+        <v>0.5364</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.6167</v>
+        <v>-3.6168</v>
       </c>
       <c r="U24" t="n">
-        <v>4.1532</v>
+        <v>4.153099999999999</v>
       </c>
       <c r="V24" t="n">
         <v>3.3788</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484344_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484344_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.1219</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484344_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-2.5591</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484344_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.6428</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484344_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,11 +881,16 @@
       <c r="X5" t="n">
         <v>-0.853</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484344_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. VIÑALLONGA BLANCO</t>
+          <t>G. VINALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,31 +902,31 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.6221</v>
+        <v>2.0151</v>
       </c>
       <c r="E6" t="n">
-        <v>2.3623</v>
+        <v>1.7553</v>
       </c>
       <c r="F6" t="n">
         <v>0.2599</v>
       </c>
       <c r="G6" t="n">
-        <v>2.7657</v>
+        <v>2.1587</v>
       </c>
       <c r="H6" t="n">
         <v>2.132</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.0266</v>
       </c>
       <c r="J6" t="n">
-        <v>2.7156</v>
+        <v>2.1086</v>
       </c>
       <c r="K6" t="n">
         <v>2.6209</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09470000000000001</v>
+        <v>-0.5122</v>
       </c>
       <c r="M6" t="n">
         <v>0.05</v>
@@ -938,6 +963,11 @@
       </c>
       <c r="X6" t="n">
         <v>-1.4959</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484344_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1017,11 +1047,16 @@
       <c r="X7" t="n">
         <v>0.0213</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484344_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. PAGES SAUQUE</t>
+          <t>G. VIÑALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4088</v>
+        <v>0.607</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9546</v>
+        <v>0.607</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5458</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0148</v>
+        <v>0.607</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.2712</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2564</v>
+        <v>0.607</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.93</v>
+        <v>0.607</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.9171</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0128</v>
+        <v>0.607</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0848</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.354</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2692</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1754</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3019</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1265</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484344_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. BELVER EDO</t>
+          <t>M. PAGES SAUQUE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8297</v>
+        <v>-0.4088</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.959</v>
+        <v>-0.9546</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1293</v>
+        <v>0.5458</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3119</v>
+        <v>-1.0148</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5513</v>
+        <v>-1.2712</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8632</v>
+        <v>0.2564</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0568</v>
+        <v>-0.93</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0025</v>
+        <v>-0.9171</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0543</v>
+        <v>-0.0128</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2551</v>
+        <v>-0.0848</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5538</v>
+        <v>-0.354</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8089</v>
+        <v>0.2692</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1953</v>
+        <v>0.7814</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3674</v>
+        <v>0.7814</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6128</v>
+        <v>-0.1754</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1562</v>
+        <v>-0.3019</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4566</v>
+        <v>0.1265</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.9498</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.9498</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484344_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. REYES QUEZADA</t>
+          <t>I. BELVER EDO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6181</v>
+        <v>-0.8297</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4121</v>
+        <v>-0.959</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.206</v>
+        <v>0.1293</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.3958</v>
+        <v>0.3119</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.802</v>
+        <v>-0.5513</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5938</v>
+        <v>0.8632</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.5717</v>
+        <v>0.0568</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.6526</v>
+        <v>0.0025</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0809</v>
+        <v>0.0543</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8241000000000001</v>
+        <v>0.2551</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1494</v>
+        <v>-0.5538</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6747</v>
+        <v>0.8089</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1721</v>
+        <v>0.1953</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1953</v>
+        <v>-1.1721</v>
       </c>
       <c r="R10" t="n">
         <v>1.3674</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6548</v>
+        <v>0.6128</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6451</v>
+        <v>0.1562</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0097</v>
+        <v>0.4566</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.7396</v>
+        <v>-1.9498</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.7396</v>
+        <v>-1.9498</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484344_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C. MARZO CHECA</t>
+          <t>A. REYES QUEZADA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.6865</v>
+        <v>-3.6181</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.4019</v>
+        <v>-2.4121</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7155</v>
+        <v>-1.206</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.7776</v>
+        <v>-2.3958</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.3927</v>
+        <v>-1.802</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.3849</v>
+        <v>-0.5938</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.8785</v>
+        <v>-1.5717</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.3035</v>
+        <v>-1.6526</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.575</v>
+        <v>0.0809</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.8992</v>
+        <v>-0.8241000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0893</v>
+        <v>-0.1494</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8099</v>
+        <v>-0.6747</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.3907</v>
+        <v>1.1721</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.1488</v>
+        <v>-0.1953</v>
       </c>
       <c r="R11" t="n">
-        <v>1.7581</v>
+        <v>1.3674</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2744</v>
+        <v>-0.6548</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3747</v>
+        <v>-0.6451</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1003</v>
+        <v>-0.0097</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2437</v>
+        <v>-1.7396</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2437</v>
+        <v>-1.7396</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484344_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>C. MARZO CHECA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,151 +1400,157 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>14.5747</v>
+        <v>-5.6865</v>
       </c>
       <c r="E12" t="n">
-        <v>1.531399999999999</v>
+        <v>-6.4019</v>
       </c>
       <c r="F12" t="n">
-        <v>13.0435</v>
+        <v>0.7155</v>
       </c>
       <c r="G12" t="n">
-        <v>8.791600000000001</v>
+        <v>-4.7776</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.998</v>
+        <v>-1.3927</v>
       </c>
       <c r="I12" t="n">
-        <v>10.7895</v>
+        <v>-3.3849</v>
       </c>
       <c r="J12" t="n">
-        <v>10.0139</v>
+        <v>-3.8785</v>
       </c>
       <c r="K12" t="n">
-        <v>1.9159</v>
+        <v>-1.3035</v>
       </c>
       <c r="L12" t="n">
-        <v>8.097999999999999</v>
+        <v>-2.575</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.2225</v>
+        <v>-0.8992</v>
       </c>
       <c r="N12" t="n">
-        <v>-3.9138</v>
+        <v>-0.0893</v>
       </c>
       <c r="O12" t="n">
-        <v>2.6914</v>
+        <v>-0.8099</v>
       </c>
       <c r="P12" t="n">
-        <v>8.7904</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q12" t="n">
-        <v>-11.7207</v>
+        <v>-2.1488</v>
       </c>
       <c r="R12" t="n">
-        <v>20.511</v>
+        <v>1.7581</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3714999999999999</v>
+        <v>-0.2744</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.2453</v>
+        <v>-0.3747</v>
       </c>
       <c r="U12" t="n">
-        <v>3.6167</v>
+        <v>0.1003</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.3786</v>
+        <v>-0.2437</v>
       </c>
       <c r="W12" t="n">
-        <v>6.483</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-9.861700000000001</v>
+        <v>-0.2437</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484344_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>G. SABATÉS SALA</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>C.B. VIC - UNIVERSITAT DE VIC</t>
+          <t>DM GROUP MOLLET</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.5716</v>
+        <v>14.5747</v>
       </c>
       <c r="E13" t="n">
-        <v>1.3646</v>
+        <v>1.531399999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2071</v>
+        <v>13.0435</v>
       </c>
       <c r="G13" t="n">
-        <v>1.1088</v>
+        <v>8.791600000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7583</v>
+        <v>-1.998</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3506</v>
+        <v>10.7895</v>
       </c>
       <c r="J13" t="n">
-        <v>1.3384</v>
+        <v>10.0139</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7176</v>
+        <v>1.915900000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6208</v>
+        <v>8.098099999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.2295</v>
+        <v>-1.2225</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0407</v>
+        <v>-3.9138</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2702</v>
+        <v>2.6914</v>
       </c>
       <c r="P13" t="n">
-        <v>1.1721</v>
+        <v>8.790399999999998</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.1953</v>
+        <v>-11.7207</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3674</v>
+        <v>20.511</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.474</v>
+        <v>0.3714999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.665</v>
+        <v>-3.2453</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1911</v>
+        <v>3.6167</v>
       </c>
       <c r="V13" t="n">
-        <v>0.7647</v>
+        <v>-3.3786</v>
       </c>
       <c r="W13" t="n">
-        <v>0.8865</v>
+        <v>6.483</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.1219</v>
-      </c>
+        <v>-9.861699999999999</v>
+      </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. VIDAL AGRA</t>
+          <t>G. SABATES SALA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1562,78 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.1569</v>
+        <v>2.2646</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6758999999999999</v>
+        <v>1.0576</v>
       </c>
       <c r="F14" t="n">
-        <v>1.481</v>
+        <v>1.2071</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0867</v>
+        <v>0.8018999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>1.045</v>
+        <v>0.4513</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.9583</v>
+        <v>0.3506</v>
       </c>
       <c r="J14" t="n">
-        <v>0.986</v>
+        <v>1.0314</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8646</v>
+        <v>0.4106</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1214</v>
+        <v>0.6208</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.8994</v>
+        <v>-0.2295</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1804</v>
+        <v>0.0407</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.0797</v>
+        <v>-0.2702</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9767</v>
+        <v>-0.1953</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7581</v>
+        <v>1.3674</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9568</v>
+        <v>-0.474</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0573</v>
+        <v>-0.665</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8995</v>
+        <v>0.1911</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3321</v>
+        <v>0.7647</v>
       </c>
       <c r="W14" t="n">
-        <v>0.6093</v>
+        <v>0.8865</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2772</v>
+        <v>-0.1219</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484344_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. VIDAL TEIXIDOR</t>
+          <t>C. VIDAL AGRA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8378</v>
+        <v>2.1569</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.1666</v>
+        <v>0.6758999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0045</v>
+        <v>1.481</v>
       </c>
       <c r="G15" t="n">
-        <v>1.0178</v>
+        <v>0.0867</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5974</v>
+        <v>1.045</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5795</v>
+        <v>-0.9583</v>
       </c>
       <c r="J15" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.986</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1241</v>
+        <v>0.8646</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.0395</v>
+        <v>0.1214</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9332</v>
+        <v>-0.8994</v>
       </c>
       <c r="N15" t="n">
-        <v>1.4733</v>
+        <v>0.1804</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5401</v>
+        <v>-1.0797</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.7814</v>
+        <v>0.7814</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.1488</v>
+        <v>-0.9767</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3674</v>
+        <v>1.7581</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3363</v>
+        <v>0.9568</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3211</v>
+        <v>0.0573</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6574</v>
+        <v>0.8995</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2651</v>
+        <v>0.3321</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2186</v>
+        <v>0.6093</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.9536</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484344_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>N. DEL VAL GARCIA</t>
+          <t>D. VIDAL TEIXIDOR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.6768</v>
+        <v>0.8378</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4829</v>
+        <v>-1.1666</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.1597</v>
+        <v>2.0045</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.6477</v>
+        <v>1.0178</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1589</v>
+        <v>1.5974</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.8065</v>
+        <v>-0.5795</v>
       </c>
       <c r="J16" t="n">
-        <v>1.144</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>1.3315</v>
+        <v>0.1241</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.1875</v>
+        <v>-0.0395</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.7917</v>
+        <v>0.9332</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1727</v>
+        <v>1.4733</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.619</v>
+        <v>-0.5401</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.3674</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9534</v>
+        <v>-2.1488</v>
       </c>
       <c r="R16" t="n">
-        <v>0.586</v>
+        <v>1.3674</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.099</v>
+        <v>0.3363</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4222</v>
+        <v>-0.3211</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3232</v>
+        <v>0.6574</v>
       </c>
       <c r="V16" t="n">
-        <v>2.4373</v>
+        <v>0.2651</v>
       </c>
       <c r="W16" t="n">
-        <v>2.7145</v>
+        <v>1.2186</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2772</v>
+        <v>-0.9536</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484344_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. TARRES HERNANDEZ</t>
+          <t>G. SABATÉS SALA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,40 +1811,40 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7352</v>
+        <v>0.307</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0801</v>
+        <v>0.307</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6551</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5034</v>
+        <v>0.307</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0987</v>
+        <v>0.307</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4047</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0409</v>
+        <v>0.307</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0409</v>
+        <v>0.307</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5443</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1397</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4047</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -1780,28 +1856,33 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0454</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.121</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1664</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484344_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. SIMS SERRA</t>
+          <t>N. DEL VAL GARCIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1395</v>
+        <v>-0.6768</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8162</v>
+        <v>1.4829</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3233</v>
+        <v>-2.1597</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4847</v>
+        <v>-1.6477</v>
       </c>
       <c r="H18" t="n">
-        <v>2.1584</v>
+        <v>0.1589</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.6431</v>
+        <v>-1.8065</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6337</v>
+        <v>1.144</v>
       </c>
       <c r="K18" t="n">
-        <v>2.6017</v>
+        <v>1.3315</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.968</v>
+        <v>-0.1875</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.1184</v>
+        <v>-2.7917</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4433</v>
+        <v>-1.1727</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6751</v>
+        <v>-1.619</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.5627</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9301</v>
+        <v>-1.9534</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3674</v>
+        <v>0.586</v>
       </c>
       <c r="S18" t="n">
-        <v>0.07630000000000001</v>
+        <v>-0.099</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5701000000000001</v>
+        <v>-0.4222</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6463</v>
+        <v>0.3232</v>
       </c>
       <c r="V18" t="n">
-        <v>0.8317</v>
+        <v>2.4373</v>
       </c>
       <c r="W18" t="n">
-        <v>2.0503</v>
+        <v>2.7145</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2186</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484344_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. CRUZ URBANEJA</t>
+          <t>G. TARRES HERNANDEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5996</v>
+        <v>-0.7352</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.8962</v>
+        <v>-0.0801</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2966</v>
+        <v>-0.6551</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8299</v>
+        <v>-0.5034</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6669</v>
+        <v>-0.0987</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.4968</v>
+        <v>-0.4047</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5502</v>
+        <v>0.0409</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6766</v>
+        <v>0.0409</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.2268</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2797</v>
+        <v>-0.5443</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0097</v>
+        <v>-0.1397</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.27</v>
+        <v>-0.4047</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.379</v>
+        <v>0.0454</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3693</v>
+        <v>-0.121</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0097</v>
+        <v>0.1664</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484344_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. PALLARES ARUMI</t>
+          <t>E. SIMS SERRA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9991</v>
+        <v>-1.1395</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7748</v>
+        <v>-0.8162</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2243</v>
+        <v>-0.3233</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.9771</v>
+        <v>-0.4847</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.8286</v>
+        <v>2.1584</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1484</v>
+        <v>-2.6431</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5437</v>
+        <v>0.6337</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.2049</v>
+        <v>2.6017</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6613</v>
+        <v>-1.968</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.4334</v>
+        <v>-1.1184</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6237</v>
+        <v>-0.4433</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8097</v>
+        <v>-0.6751</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3907</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R20" t="n">
-        <v>0.586</v>
+        <v>1.3674</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3687</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2544</v>
+        <v>-0.5701000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6231</v>
+        <v>0.6463</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.8317</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.0503</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484344_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>O. SUBIRANAS CASELLAS</t>
+          <t>M. CRUZ URBANEJA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0898</v>
+        <v>-1.5996</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5108</v>
+        <v>-1.8962</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4211</v>
+        <v>0.2966</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.5785</v>
+        <v>-0.8299</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1734</v>
+        <v>0.6669</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4051</v>
+        <v>-1.4968</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0409</v>
+        <v>-0.5502</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0409</v>
+        <v>0.6766</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-1.2268</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6194</v>
+        <v>-0.2797</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2144</v>
+        <v>-0.0097</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4051</v>
+        <v>-0.27</v>
       </c>
       <c r="P21" t="n">
+        <v>-0.3907</v>
+      </c>
+      <c r="Q21" t="n">
         <v>-0.9767</v>
       </c>
-      <c r="Q21" t="n">
-        <v>-2.1488</v>
-      </c>
       <c r="R21" t="n">
-        <v>1.1721</v>
+        <v>0.586</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4127</v>
+        <v>-0.379</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.403</v>
+        <v>-0.3693</v>
       </c>
       <c r="U21" t="n">
         <v>-0.0097</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1219</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1219</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484344_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. LAJAY BOBEPARI</t>
+          <t>F. PALLARES ARUMI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.1251</v>
+        <v>-1.9991</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.4268</v>
+        <v>-1.7748</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6983</v>
+        <v>-0.2243</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.0319</v>
+        <v>-1.9771</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.6961</v>
+        <v>-1.8286</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.3358</v>
+        <v>-0.1484</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.3088</v>
+        <v>-0.5437</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.3227</v>
+        <v>-1.2049</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0138</v>
+        <v>0.6613</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.723</v>
+        <v>-1.4334</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3735</v>
+        <v>-0.6237</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.3496</v>
+        <v>-0.8097</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.1255</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q22" t="n">
-        <v>-5.0789</v>
+        <v>-0.9767</v>
       </c>
       <c r="R22" t="n">
-        <v>1.9534</v>
+        <v>0.586</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2676</v>
+        <v>0.3687</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4215</v>
+        <v>-0.2544</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.6231</v>
       </c>
       <c r="V22" t="n">
-        <v>0.7647</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>2.3824</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.6177</v>
+        <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484344_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. CANAL FERRER</t>
+          <t>O. SUBIRANAS CASELLAS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.8682</v>
+        <v>-2.0898</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.8954</v>
+        <v>-2.5108</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.9728</v>
+        <v>0.4211</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.9517</v>
+        <v>-0.5785</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5899</v>
+        <v>-0.1734</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.3618</v>
+        <v>-0.4051</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6435</v>
+        <v>0.0409</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0435</v>
+        <v>0.0409</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6869</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.3083</v>
+        <v>-0.6194</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.6334</v>
+        <v>-0.2144</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6749000000000001</v>
+        <v>-0.4051</v>
       </c>
       <c r="P23" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="Q23" t="n">
         <v>-2.1488</v>
       </c>
-      <c r="Q23" t="n">
-        <v>-3.1255</v>
-      </c>
       <c r="R23" t="n">
-        <v>0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.15</v>
+        <v>-0.4127</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1265</v>
+        <v>-0.403</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0235</v>
+        <v>-0.0097</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.6177</v>
+        <v>-0.1219</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.6177</v>
+        <v>-0.1219</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484344_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. LAJAY BOBEPARI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,68 +2392,235 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
+        <v>-5.1251</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-4.4268</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-0.6983</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-3.0319</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-1.6961</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-1.3358</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-1.3088</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-1.3227</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.0138</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-1.723</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.3735</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-1.3496</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-3.1255</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-5.0789</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.9534</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.2676</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.4215</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0.7647</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.3824</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-1.6177</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484344_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>J. CANAL FERRER</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>C.B. VIC - UNIVERSITAT DE VIC</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-5.8682</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-3.8954</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-1.9728</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-1.9517</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.5899</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-1.3618</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-0.6435</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.0435</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-0.6869</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-1.3083</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.6334</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.6749000000000001</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-2.1488</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-3.1255</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.1265</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.0235</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-1.6177</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-1.6177</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484344_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>C.B. VIC - UNIVERSITAT DE VIC</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
         <v>-13.667</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E26" t="n">
         <v>-13.0435</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F26" t="n">
         <v>-0.6231999999999995</v>
       </c>
-      <c r="G24" t="n">
-        <v>-8.791600000000001</v>
-      </c>
-      <c r="H24" t="n">
+      <c r="G26" t="n">
+        <v>-8.791500000000001</v>
+      </c>
+      <c r="H26" t="n">
         <v>1.998199999999999</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I26" t="n">
         <v>-10.7894</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J26" t="n">
         <v>1.2223</v>
       </c>
-      <c r="K24" t="n">
-        <v>3.913799999999999</v>
-      </c>
-      <c r="L24" t="n">
+      <c r="K26" t="n">
+        <v>3.9138</v>
+      </c>
+      <c r="L26" t="n">
         <v>-2.6914</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M26" t="n">
         <v>-10.0139</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N26" t="n">
         <v>-1.916</v>
       </c>
-      <c r="O24" t="n">
-        <v>-8.098099999999999</v>
-      </c>
-      <c r="P24" t="n">
+      <c r="O26" t="n">
+        <v>-8.098100000000001</v>
+      </c>
+      <c r="P26" t="n">
         <v>-8.7904</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q26" t="n">
         <v>-20.5109</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R26" t="n">
         <v>11.7205</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S26" t="n">
         <v>0.5364</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T26" t="n">
         <v>-3.6168</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U26" t="n">
         <v>4.153099999999999</v>
       </c>
-      <c r="V24" t="n">
+      <c r="V26" t="n">
         <v>3.3788</v>
       </c>
-      <c r="W24" t="n">
+      <c r="W26" t="n">
         <v>9.861600000000001</v>
       </c>
-      <c r="X24" t="n">
+      <c r="X26" t="n">
         <v>-6.483000000000001</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
